--- a/results_combat/solution_biodiverse.xlsx
+++ b/results_combat/solution_biodiverse.xlsx
@@ -23257,7 +23257,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="H7" t="n">
         <v>46.8</v>
@@ -26284,7 +26284,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="116">
@@ -28341,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>100</v>
+        <v>42.1658</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>100</v>
+        <v>17.1528</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -28717,7 +28717,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>54.1935</v>
+        <v>53.6935</v>
       </c>
       <c r="H202" t="n">
         <v>45.8065</v>
@@ -29193,7 +29193,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>65.16849999999999</v>
+        <v>64.66849999999999</v>
       </c>
       <c r="H219" t="n">
         <v>34.8315</v>
@@ -30005,7 +30005,7 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>56.9713</v>
+        <v>56.4713</v>
       </c>
       <c r="H248" t="n">
         <v>43.0287</v>
@@ -30033,7 +30033,7 @@
         <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>75.6549</v>
+        <v>75.1549</v>
       </c>
       <c r="H249" t="n">
         <v>24.3451</v>
@@ -30285,7 +30285,7 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>58.4932</v>
+        <v>57.9932</v>
       </c>
       <c r="H258" t="n">
         <v>41.5068</v>
@@ -30313,7 +30313,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>65.9513</v>
+        <v>65.4513</v>
       </c>
       <c r="H259" t="n">
         <v>34.0487</v>
@@ -30957,7 +30957,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>61.3674</v>
+        <v>60.8674</v>
       </c>
       <c r="H282" t="n">
         <v>38.6326</v>
@@ -31741,7 +31741,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>99.8353</v>
+        <v>99.5</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -32049,7 +32049,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>62.6301</v>
+        <v>62.1301</v>
       </c>
       <c r="H321" t="n">
         <v>37.3699</v>
@@ -33141,7 +33141,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>57.2708</v>
+        <v>56.7708</v>
       </c>
       <c r="H360" t="n">
         <v>42.7292</v>
@@ -33253,7 +33253,7 @@
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>54.5455</v>
+        <v>54.0455</v>
       </c>
       <c r="H364" t="n">
         <v>45.4545</v>
@@ -33729,7 +33729,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>50.7667</v>
+        <v>50.2667</v>
       </c>
       <c r="H381" t="n">
         <v>49.2333</v>
@@ -33757,7 +33757,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>61.3647</v>
+        <v>60.8647</v>
       </c>
       <c r="H382" t="n">
         <v>38.6353</v>
@@ -34289,7 +34289,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>61.4286</v>
+        <v>60.9286</v>
       </c>
       <c r="H401" t="n">
         <v>38.5714</v>
@@ -34457,7 +34457,7 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>42.268</v>
+        <v>41.768</v>
       </c>
       <c r="H407" t="n">
         <v>57.732</v>
@@ -34569,7 +34569,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>70.48050000000001</v>
+        <v>69.98050000000001</v>
       </c>
       <c r="H411" t="n">
         <v>29.5195</v>
@@ -36053,7 +36053,7 @@
         <v>0</v>
       </c>
       <c r="G464" t="n">
-        <v>47.1642</v>
+        <v>46.6642</v>
       </c>
       <c r="H464" t="n">
         <v>52.8358</v>
@@ -38072,7 +38072,7 @@
         <v>0</v>
       </c>
       <c r="H536" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="537">
